--- a/LISTAS/mi/PLANCHUELA DISMAY.xlsx
+++ b/LISTAS/mi/PLANCHUELA DISMAY.xlsx
@@ -714,14 +714,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="n">
-        <v>45163.60908132227</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45253</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="16">
       <c r="A7" s="22" t="inlineStr">
         <is>
@@ -804,7 +799,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>36.266</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="16">
@@ -822,7 +817,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>47.305</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="16">
@@ -840,7 +835,7 @@
         <v>50</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>56.542</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="16">
@@ -858,7 +853,7 @@
         <v>50</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>81.994</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" s="16">
@@ -876,7 +871,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>102.265</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" s="16">
@@ -894,7 +889,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>127.492</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" s="16">
@@ -912,7 +907,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>142.586</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" s="16">
@@ -930,31 +925,12 @@
         <v>50</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>158.806</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
+        <v>185</v>
+      </c>
+    </row>
     <row r="30">
       <c r="E30" s="14" t="n"/>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
@@ -964,10 +940,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/PLANCHUELA DISMAY.xlsx
+++ b/LISTAS/mi/PLANCHUELA DISMAY.xlsx
@@ -714,7 +714,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="16">

--- a/LISTAS/mi/PLANCHUELA DISMAY.xlsx
+++ b/LISTAS/mi/PLANCHUELA DISMAY.xlsx
@@ -714,7 +714,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="16">

--- a/LISTAS/mi/PLANCHUELA DISMAY.xlsx
+++ b/LISTAS/mi/PLANCHUELA DISMAY.xlsx
@@ -714,9 +714,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45254.59211992285</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1" s="16">
       <c r="A7" s="22" t="inlineStr">
         <is>
@@ -799,7 +804,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>38.5</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="16">
@@ -817,7 +822,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>50.1</v>
+        <v>64.47</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="16">
@@ -835,7 +840,7 @@
         <v>50</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>60</v>
+        <v>77.22</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="16">
@@ -853,7 +858,7 @@
         <v>50</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>96</v>
+        <v>123.55</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" s="16">
@@ -871,7 +876,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>120</v>
+        <v>154.44</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" s="16">
@@ -889,7 +894,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>150</v>
+        <v>193.05</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" s="16">
@@ -907,7 +912,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>167</v>
+        <v>214.92</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" s="16">
@@ -925,12 +930,31 @@
         <v>50</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>185</v>
-      </c>
-    </row>
+        <v>238.09</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="E30" s="14" t="n"/>
     </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
@@ -940,10 +964,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/PLANCHUELA DISMAY.xlsx
+++ b/LISTAS/mi/PLANCHUELA DISMAY.xlsx
@@ -714,14 +714,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="n">
-        <v>45254.59211992285</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45286</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="16">
       <c r="A7" s="22" t="inlineStr">
         <is>
@@ -804,7 +799,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>49.55</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="16">
@@ -822,7 +817,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>64.47</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="16">
@@ -840,7 +835,7 @@
         <v>50</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>77.22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="16">
@@ -858,7 +853,7 @@
         <v>50</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>123.55</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" s="16">
@@ -876,7 +871,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>154.44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" s="16">
@@ -894,7 +889,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>193.05</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" s="16">
@@ -912,7 +907,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>214.92</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" s="16">
@@ -930,31 +925,12 @@
         <v>50</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>238.09</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
+        <v>185</v>
+      </c>
+    </row>
     <row r="30">
       <c r="E30" s="14" t="n"/>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
@@ -964,10 +940,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
